--- a/62730_smc_model.xlsx
+++ b/62730_smc_model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wenjun/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F91B5AC-FEA3-2448-969E-6185AA60F073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F0F98D-190A-B941-94D9-F29ED0894979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6460" yWindow="600" windowWidth="37320" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6460" yWindow="600" windowWidth="37320" windowHeight="21000" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Drivers" sheetId="1" r:id="rId1"/>
@@ -1694,8 +1694,8 @@
     <numFmt numFmtId="183" formatCode="0.0000"/>
     <numFmt numFmtId="184" formatCode="#,##0_);[Red]\(#,##0\);&quot;–&quot;"/>
     <numFmt numFmtId="185" formatCode="0.0&quot;x&quot;_);[Red]\(0.0&quot;x&quot;\);&quot;–&quot;"/>
-    <numFmt numFmtId="188" formatCode="0.0"/>
-    <numFmt numFmtId="189" formatCode="0.0;[Red]\-0.0;&quot;OK&quot;"/>
+    <numFmt numFmtId="186" formatCode="0.0"/>
+    <numFmt numFmtId="187" formatCode="0.0;[Red]\-0.0;&quot;OK&quot;"/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -2013,13 +2013,13 @@
     <xf numFmtId="176" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="179" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="188" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="186" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="184" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="184" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="186" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="189" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="184" fontId="12" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="179" fontId="12" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -4350,7 +4350,7 @@
         <v>592.44876517896409</v>
       </c>
       <c r="M8" s="13">
-        <f t="shared" ref="J8:Q8" si="5">M4*0.195</f>
+        <f t="shared" ref="M8:Q8" si="5">M4*0.195</f>
         <v>566.08479512850022</v>
       </c>
       <c r="N8" s="13">
@@ -15318,8 +15318,8 @@
         <v>528</v>
       </c>
       <c r="B14" s="80">
-        <f>3000*25</f>
-        <v>75000</v>
+        <f>3500*25</f>
+        <v>87500</v>
       </c>
       <c r="C14" s="89">
         <f t="shared" ref="C14:C15" si="0">0.333333333333333%*100</f>
@@ -15355,7 +15355,7 @@
       </c>
       <c r="B16" s="91">
         <f>SUMPRODUCT(B13:B15,C13:C15)</f>
-        <v>78333.333333333256</v>
+        <v>82499.999999999913</v>
       </c>
       <c r="C16" s="90">
         <f>SUM(C13:C15)</f>
@@ -15383,7 +15383,7 @@
       </c>
       <c r="B18" s="92">
         <f>B16/B17-1</f>
-        <v>0.15382726960278759</v>
+        <v>0.21520106053910615</v>
       </c>
       <c r="C18" s="90"/>
       <c r="D18" s="2"/>
